--- a/analise_eua/tecnologia/microsoft/msft_10q.xlsx
+++ b/analise_eua/tecnologia/microsoft/msft_10q.xlsx
@@ -24,13 +24,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,13 +52,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,2217 +435,2316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44561</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44196</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43921</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43830</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>32105</v>
+      </c>
+      <c r="C2" t="n">
         <v>24296</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>28849</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>28828</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>17482</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>20840</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>19634</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>17305</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>80452</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>26562</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>15646</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>22884</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>12498</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>20604</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>19165</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>13702</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>14432</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>17205</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>11710</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>8864</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>13117</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Short-term Investments</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C3" t="n">
         <v>65166</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>73163</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>50790</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>54073</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>57588</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>60387</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>63712</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>63499</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>77865</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>83862</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>84378</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>92195</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>104765</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>111450</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>111705</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>117536</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>120772</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>125916</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>125389</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>123519</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, and Short-term Investments</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>78272</v>
+      </c>
+      <c r="C4" t="n">
         <v>89462</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>102012</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>79618</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>71555</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>78428</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>80021</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>81017</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>143951</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>104427</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>99508</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>107262</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>104693</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>125369</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>130615</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>125407</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>131968</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>137977</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>137626</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>134253</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>136636</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Accounts Receivable, after Allowance for Credit Loss, Current</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>60041</v>
+      </c>
+      <c r="C5" t="n">
         <v>56535</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>52894</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>51700</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>48188</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>44148</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>44029</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>42831</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>36953</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>37420</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>35833</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>31279</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>32613</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>33520</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>27349</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>26322</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>27312</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>22851</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>22699</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>23525</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>19087</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1219</v>
+      </c>
+      <c r="C6" t="n">
         <v>1059</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1130</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>848</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>909</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1626</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1304</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1615</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>3000</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>2877</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2980</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>4268</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3296</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>3019</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>3411</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>2245</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1924</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>2705</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1644</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1823</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>2622</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Current</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>35797</v>
+      </c>
+      <c r="C7" t="n">
         <v>33134</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>33030</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>24478</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>26428</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>25724</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>21826</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>21930</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>23682</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>19165</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>19502</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>18003</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>13320</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12280</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>12951</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>11640</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>12769</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>13544</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8536</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>7473</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>7551</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Assets, Current</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>175329</v>
+      </c>
+      <c r="C8" t="n">
         <v>180190</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>189066</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>156644</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>147080</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>149926</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>147180</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>147393</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>207586</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>163889</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>157823</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>160812</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>153922</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>174188</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>174326</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>165614</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>173973</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>177077</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>170505</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>167074</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>165896</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment, Net</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>283228</v>
+      </c>
+      <c r="C9" t="n">
         <v>261126</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>230861</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>183939</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>166902</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>152863</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>121375</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>112308</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>102502</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>88132</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>82755</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>77037</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>70298</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>67214</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>63772</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>54945</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>51737</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>47927</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>41221</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>40522</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>38409</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Operating Lease, Right-of-Use Asset</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>24403</v>
+      </c>
+      <c r="C10" t="n">
         <v>25103</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>24791</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>24475</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>22816</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20528</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>17371</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>16398</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>15435</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>13879</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>13624</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>13347</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>12916</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>12354</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11575</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>10673</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>10298</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>9047</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>8448</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>8439</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>7890</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Equity and Other Investments</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>33683</v>
+      </c>
+      <c r="C11" t="n">
         <v>21202</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>11465</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>16035</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>15581</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>15778</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>14807</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>13367</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>11423</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>9415</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7097</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>6839</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>6907</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>6994</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>6393</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>5395</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>3794</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>3103</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>2660</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2755</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>2684</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>119661</v>
+      </c>
+      <c r="C12" t="n">
         <v>119622</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>119497</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>119329</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>119191</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>119374</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>119163</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>118931</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>67790</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>67940</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>67905</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>67459</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>67371</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>50921</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>50455</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>49698</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>44219</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>43890</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>42064</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>42248</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>42113</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Finite-Lived Intangible Assets, Net</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>19325</v>
+      </c>
+      <c r="C13" t="n">
         <v>20289</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>21236</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>23968</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>25385</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>26751</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>28828</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>29896</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>8895</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>9879</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>10354</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>10808</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>11348</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>7462</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>7794</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>8127</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>6555</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>6923</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>6855</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>7126</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>7508</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Noncurrent</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>38599</v>
+      </c>
+      <c r="C14" t="n">
         <v>37770</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>39435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>38234</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>36943</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>37793</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>35551</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>32265</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>32154</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>26954</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>24994</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>23482</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>21845</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>21256</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>21103</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>14427</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>13561</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>13034</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>13696</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>14630</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>14455</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>694228</v>
+      </c>
+      <c r="C15" t="n">
         <v>665302</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>636351</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>562624</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>533898</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>523013</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>484275</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>470558</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>445785</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>380088</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>364552</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>359784</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>344607</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>340389</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>335418</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>308879</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>304137</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>301001</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>285449</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>282794</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>278955</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Accounts Payable, Current</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>37513</v>
+      </c>
+      <c r="C16" t="n">
         <v>37328</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>32580</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>26250</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>22608</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>22768</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>18087</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>17695</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>19307</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>15305</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>15354</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>16609</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16085</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>15314</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>14832</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>13412</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>12770</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>12509</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>9246</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>8811</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>8574</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Current Portion of Long-term Debt</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>8839</v>
+      </c>
+      <c r="C17" t="n">
         <v>4837</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>7832</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>2999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>5248</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2249</v>
       </c>
       <c r="G17" t="n">
         <v>2249</v>
       </c>
       <c r="H17" t="n">
+        <v>2249</v>
+      </c>
+      <c r="I17" t="n">
         <v>2250</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>3748</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>6245</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>3997</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>3248</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1749</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>4998</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>3249</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>8051</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>5387</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>6497</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>3748</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>6247</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>3017</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Employee-related Liabilities, Current</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>11270</v>
+      </c>
+      <c r="C18" t="n">
         <v>10103</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>9201</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>10579</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>9176</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>8326</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>10432</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>8813</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>6990</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>10411</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>9030</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>7405</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>9067</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>7782</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>6894</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>8032</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>6838</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>5714</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>6254</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>5421</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>4676</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Accrued Income Taxes, Current</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>3563</v>
+      </c>
+      <c r="C19" t="n">
         <v>2050</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>3655</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>6805</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>6056</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>9717</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>7311</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5787</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>8035</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>4163</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>3553</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>6729</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>4646</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3731</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>6272</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>2165</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>1562</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>2384</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>3296</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>2687</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>3440</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Contract with Customer, Liability, Current</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>50924</v>
+      </c>
+      <c r="C20" t="n">
         <v>51376</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>58987</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>44636</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>45508</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>53026</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>41888</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>43068</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>46429</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>36903</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>36982</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>41340</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>34027</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>34001</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>38465</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>30083</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30402</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>33476</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>27012</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>27343</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>29904</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Current</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>24552</v>
+      </c>
+      <c r="C21" t="n">
         <v>24311</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>22741</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>22937</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>20286</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>19114</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>18023</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>16362</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>14475</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>12664</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>12802</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>12058</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>11865</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>11684</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>10816</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>10450</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>10527</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>9476</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>9151</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>9131</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>8507</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>136661</v>
+      </c>
+      <c r="C22" t="n">
         <v>130005</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>134996</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>114206</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>108882</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>115200</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>118525</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>121016</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>124792</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>85691</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>81718</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>87389</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>77439</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>77510</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>80528</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>72193</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>67486</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>70056</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>58707</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>59640</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>58118</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Long-term debt</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>31423</v>
+      </c>
+      <c r="C23" t="n">
         <v>35425</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>35376</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>39882</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>39722</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>42868</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>42658</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>44928</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>41946</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>41965</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>44119</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>45374</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>48177</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>48260</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>50039</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>50007</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>55136</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>57055</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>62862</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>63361</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>66478</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Accrued Income Taxes, Noncurrent</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>27941</v>
+      </c>
+      <c r="C24" t="n">
         <v>27256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>26569</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>25061</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>24389</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>24452</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>26786</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>25890</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>22983</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>25000</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>24169</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>23712</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>26483</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>26121</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>25715</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>27157</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>26701</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>28204</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>28888</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>28754</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>28457</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Contract with Customer, Liability, Noncurrent</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2753</v>
+      </c>
+      <c r="C25" t="n">
         <v>2668</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>2546</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>2840</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>2537</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>2663</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>2945</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>2966</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>2759</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2698</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>2644</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2549</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>2769</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>2768</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2550</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>2631</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>2985</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>2829</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>3385</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>3878</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>4122</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Deferred Income Tax Liabilities, Net</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2899</v>
+      </c>
+      <c r="C26" t="n">
         <v>2876</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>2852</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>2522</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>2513</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>2581</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>2469</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>2548</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>470</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>302</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>289</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>223</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>304</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>199</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>212</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>173</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>174</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>187</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>185</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>222</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>234</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Operating Lease, Liability, Noncurrent</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>16703</v>
+      </c>
+      <c r="C27" t="n">
         <v>17345</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>17348</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>17686</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>17254</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>16361</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>14469</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>14155</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>13487</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>12312</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>11998</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>11660</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>11357</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>10774</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>10050</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>9272</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>8875</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>7753</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>7248</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>7172</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>6659</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>61481</v>
+      </c>
+      <c r="C28" t="n">
         <v>58852</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>53588</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>38536</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>35906</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>31165</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>23271</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>20787</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>18634</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>17437</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>16479</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>15311</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>15154</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>14747</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>14346</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>12941</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>12544</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>11525</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>9673</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>9658</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>8826</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>279861</v>
+      </c>
+      <c r="C29" t="n">
         <v>274427</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>273275</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>240733</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>231203</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>235290</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>231123</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>232290</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>225071</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>185405</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>181416</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>186218</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>181683</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>180379</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>183440</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>174374</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>173901</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>177609</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>170948</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>172685</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>172894</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Common Stocks, Including Additional Paid in Capital</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>115069</v>
+      </c>
+      <c r="C30" t="n">
         <v>112788</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>110964</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>106965</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>104829</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>102976</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>99193</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>97480</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>95508</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>92093</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>90225</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>88535</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>85767</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>84528</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>83751</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>82308</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>81896</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>81089</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>79813</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>79625</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>78882</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>302526</v>
+      </c>
+      <c r="C31" t="n">
         <v>280789</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>254873</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>219759</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>203482</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>188929</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>159394</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>145737</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>132143</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>108234</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>99368</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>92374</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>79633</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>75045</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>66944</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>50735</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>44973</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>39193</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>32012</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>30739</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>27240</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>-3228</v>
+      </c>
+      <c r="C32" t="n">
         <v>-2702</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>-2761</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>-4833</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>-5616</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>-4182</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>-5435</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>-4949</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>-6937</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>-5644</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>-6457</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>-7343</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>-2476</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>437</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1283</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>1462</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3367</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>3110</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>2676</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-255</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>-61</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>414367</v>
+      </c>
+      <c r="C33" t="n">
         <v>390875</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>363076</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>321891</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>302695</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>287723</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>253152</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>238268</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>220714</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>194683</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>183136</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>173566</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>162924</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>160010</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>151978</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>134505</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>130236</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>123392</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>114501</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>110109</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>106061</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Commercial Paper</t>
         </is>
@@ -2652,17 +2765,17 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>20535</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>27041</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>25808</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
@@ -2694,6 +2807,9 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2708,1073 +2824,1121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44561</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44196</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43921</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43830</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>82886</v>
+      </c>
+      <c r="C2" t="n">
         <v>81273</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>77673</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>70066</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>69632</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>65585</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>61858</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>62020</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>56517</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>52857</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>52747</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>50122</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>49360</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>51728</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>45317</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>41706</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>43076</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>37154</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>35021</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>36906</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>33055</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Cost of Goods and Services Sold</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>26828</v>
+      </c>
+      <c r="C3" t="n">
         <v>25978</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>24043</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>21919</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>21799</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>20099</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>18505</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>19623</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>16302</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>16128</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>17488</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>15452</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>15615</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>16960</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>13646</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>13045</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>14194</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>11002</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>10975</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>12358</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>10406</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>56058</v>
+      </c>
+      <c r="C4" t="n">
         <v>55295</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>53630</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>48147</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>47833</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>45486</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>43353</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>42397</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>40215</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>36729</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>35259</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>34670</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>33745</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>34768</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>31671</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>28661</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>28882</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>26152</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>24046</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>24548</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>22649</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Research and Development</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>8915</v>
+      </c>
+      <c r="C5" t="n">
         <v>8504</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8146</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8198</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>7917</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>7544</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>7653</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>7142</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>6659</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>6984</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>6844</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6628</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6306</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>5758</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5599</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5204</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>4899</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>4926</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>4887</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4603</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>4565</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Selling and Marketing Expense</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>6814</v>
+      </c>
+      <c r="C6" t="n">
         <v>6584</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>5717</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6212</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6440</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>5717</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6207</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>6246</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5187</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5750</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>5679</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>5126</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>5595</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>5379</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>4547</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5082</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>4947</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>4231</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>4911</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>4933</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>4337</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>General and Administrative Expense</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1931</v>
+      </c>
+      <c r="C7" t="n">
         <v>1932</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1806</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1737</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1823</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1673</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1912</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1977</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1474</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>1643</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2337</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1398</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1480</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>1384</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1287</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1327</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>1139</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>1119</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1273</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1121</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>1061</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>38398</v>
+      </c>
+      <c r="C8" t="n">
         <v>38275</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>37961</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>32000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>31653</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>30552</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>27581</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>27032</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>26895</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>22352</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>20399</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>21518</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>20364</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>22247</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>20238</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>17048</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>17897</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>15876</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>12975</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>13891</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>12686</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>942</v>
+      </c>
+      <c r="C9" t="n">
         <v>9971</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-3660</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-623</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-2288</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-283</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-854</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-506</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>389</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>321</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-60</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>54</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-174</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>268</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>286</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>188</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>440</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>248</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-132</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>194</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>39340</v>
+      </c>
+      <c r="C10" t="n">
         <v>48246</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>34301</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>31377</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>29365</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>30269</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>26727</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>26526</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>27284</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>22673</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>20339</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>21572</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>20190</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>22515</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>20524</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>17236</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>18337</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>16124</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>12843</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>14085</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>12686</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>7562</v>
+      </c>
+      <c r="C11" t="n">
         <v>9788</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>6554</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>5553</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>5257</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>5602</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4788</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4656</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4993</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>4374</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>3914</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>4016</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>3462</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>3750</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>19</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1779</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>2874</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>2231</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>2091</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2436</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>2008</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>31778</v>
+      </c>
+      <c r="C12" t="n">
         <v>38458</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>27747</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>25824</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>24108</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>24667</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>21939</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>21870</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>22291</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>18299</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>16425</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>17556</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>16728</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>18765</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>20505</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>15457</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>15463</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>13893</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>10752</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>11649</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10678</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="C13" t="n">
         <v>5.18</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>3.73</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>3.47</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>3.24</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>3.32</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>2.95</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>2.94</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>2.46</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>2.2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2.35</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2.23</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.5</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2.73</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
         <v>2.05</v>
       </c>
       <c r="R13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S13" t="n">
         <v>1.84</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>1.41</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.53</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C14" t="n">
         <v>5.16</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>3.72</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>3.46</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>3.23</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>3.3</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2.94</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2.93</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2.99</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2.45</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2.2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2.35</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2.22</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.48</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2.71</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
         <v>2.03</v>
       </c>
       <c r="R14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S14" t="n">
         <v>1.82</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.51</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>1.38</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>7426</v>
+      </c>
+      <c r="C15" t="n">
         <v>7431</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>7433</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>7434</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>7435</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>7433</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>7431</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>7432</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>7429</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>7441</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>7451</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>7457</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>7493</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>7505</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>7513</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>7539</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>7555</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>7566</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>7602</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>7621</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>7634</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>7445</v>
+      </c>
+      <c r="C16" t="n">
         <v>7460</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>7466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>7461</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>7468</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>7470</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>7472</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>7468</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7462</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>7464</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>7473</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>7485</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>7534</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>7555</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>7567</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>7597</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>7616</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>7637</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>7675</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>7691</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>7710</v>
       </c>
     </row>
@@ -3789,1078 +3953,1126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44561</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44196</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43921</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43830</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Net Income (Loss) Attributable to Parent</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>31778</v>
+      </c>
+      <c r="C2" t="n">
         <v>38458</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>27747</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>25824</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>24108</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>24667</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>21939</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>21870</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>22291</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>18299</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>16425</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>17556</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>16728</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>18765</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>20505</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>15457</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>15463</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>13893</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>10752</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>11649</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>10678</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10167</v>
+      </c>
+      <c r="C3" t="n">
         <v>9198</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>13061</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8740</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>6827</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>7383</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>6027</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5959</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3921</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>3549</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3648</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2790</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3773</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>3496</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>3212</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2936</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2761</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>2645</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3118</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3203</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>2971</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>3081</v>
+      </c>
+      <c r="C4" t="n">
         <v>3219</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>2983</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2980</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3089</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2832</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2703</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2828</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2507</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>2465</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2538</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2192</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1906</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1897</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1702</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1525</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1566</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1456</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1338</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1340</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1262</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Gain Loss On Investments And Derivative Instruments</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="C5" t="n">
         <v>-9931</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>-1007</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-298</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>976</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-125</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>49</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>198</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-40</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>214</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-22</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>105</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-307</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-364</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>-351</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>-354</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>-128</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>52</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-203</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Deferred Income Tax Expense (Benefit)</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Deferred Income Taxes and Tax Credits</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4446</v>
+        <v>2602</v>
       </c>
       <c r="C6" t="n">
-        <v>2491</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-2244</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1158</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1433</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1323</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-1702</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-568</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-1675</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-1305</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1191</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-5970</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-88</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-206</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-177</v>
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Receivable</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-4707</v>
+      </c>
+      <c r="C7" t="n">
         <v>-3436</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>16490</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>-2461</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-5978</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>14037</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-2028</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-2951</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>11034</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-1408</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-3164</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>11729</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>857</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-5543</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>10486</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>290</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-4008</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>8843</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>891</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>-4203</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>10090</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-161</v>
+      </c>
+      <c r="C8" t="n">
         <v>70</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-192</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>52</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>711</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-373</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>260</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1474</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-505</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>106</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1305</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-543</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-279</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>394</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-777</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-329</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>788</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-808</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>181</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>799</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-561</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Current Assets</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>758</v>
+      </c>
+      <c r="C9" t="n">
         <v>619</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-1162</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1076</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-353</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-82</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>951</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>725</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-796</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1152</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-392</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-332</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>91</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>830</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>940</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>478</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>730</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-54</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>94</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>165</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-438</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Noncurrent Assets</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-932</v>
+      </c>
+      <c r="C10" t="n">
         <v>-1288</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-394</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-518</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-1089</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-1761</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-2137</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-1427</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-2013</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-554</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-65</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-666</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-724</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-908</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-598</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-885</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-1499</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-62</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>124</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-517</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-333</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2320</v>
+      </c>
+      <c r="C11" t="n">
         <v>1197</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-614</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1179</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>958</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-916</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>648</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-2521</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1214</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-407</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-2058</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-1567</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>520</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>235</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-471</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>833</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>33</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>315</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>546</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-7</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>-547</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Contract with Customer, Liability</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-166</v>
+      </c>
+      <c r="C12" t="n">
         <v>-7483</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-5418</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-1032</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-6338</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-5553</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-645</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-5538</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-4126</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-181</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-5186</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-3322</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-209</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-4343</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-2885</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-473</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-3227</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>-3064</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-736</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-2936</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-2892</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Income Taxes Payable</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2296</v>
+      </c>
+      <c r="C13" t="n">
         <v>-920</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-2944</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1298</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-3395</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1016</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>2622</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-1554</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1425</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1414</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-2863</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>410</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1091</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-2057</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2653</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1074</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-2368</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-983</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>765</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-471</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-3336</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Current Liabilities</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2539</v>
+      </c>
+      <c r="C14" t="n">
         <v>2802</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>-5507</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>2839</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>3217</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-5479</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2803</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1518</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-4106</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1715</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1819</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-4024</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1287</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1745</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-4143</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1590</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1755</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>-2951</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>695</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1489</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-3320</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Noncurrent Liabilities</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-1616</v>
+      </c>
+      <c r="C15" t="n">
         <v>-1193</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-477</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-391</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>716</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-33</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>48</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-26</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>291</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>257</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>188</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>438</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>93</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>250</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>122</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>893</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>244</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-110</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>425</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>46679</v>
+      </c>
+      <c r="C16" t="n">
         <v>35758</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>45057</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>37044</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>22291</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>34180</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>31917</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>18853</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>30583</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>24441</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>11173</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>23198</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>25386</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>14480</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>24540</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>22179</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>12516</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>19335</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>17504</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>10680</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>13818</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Repayments of Short-term Debt, Maturing in Three Months or Less</t>
         </is>
@@ -4925,1277 +5137,1407 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Repayments of Debt, Maturing in More than Three Months</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
         <v>-3000</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>-2250</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>-966</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-11589</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-2916</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-1500</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>-750</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-1000</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-4197</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>-4826</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>-500</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>-3250</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>-3000</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-18</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-2500</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Issuance of Common Stock</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>541</v>
+      </c>
+      <c r="C19" t="n">
         <v>259</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>689</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>546</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>256</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>706</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>522</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>261</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>685</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>536</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>243</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>575</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>477</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>291</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>612</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>396</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>302</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>545</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>342</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>234</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>427</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-4627</v>
+      </c>
+      <c r="C20" t="n">
         <v>-7415</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-5650</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-4781</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-4986</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-4107</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-4213</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-4000</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-4831</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-5509</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-5459</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-5573</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-8822</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-7433</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-7684</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>-6930</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>-6535</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>-6743</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-7059</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-5206</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-4912</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-6756</v>
+      </c>
+      <c r="C21" t="n">
         <v>-6762</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-6169</v>
       </c>
       <c r="D21" t="n">
         <v>-6169</v>
       </c>
       <c r="E21" t="n">
+        <v>-6169</v>
+      </c>
+      <c r="F21" t="n">
         <v>-6170</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-5574</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-5572</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-5574</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-5051</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-5059</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-5066</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-4621</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-4645</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-4652</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-4206</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-4221</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-4230</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-3856</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-3876</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-3886</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>-3510</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-509</v>
+      </c>
+      <c r="C22" t="n">
         <v>-699</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>-669</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-382</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-343</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-889</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-498</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-201</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-307</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-258</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-317</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-264</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-158</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-192</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-172</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-183</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>79</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-235</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-1052</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-39</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-11351</v>
+      </c>
+      <c r="C23" t="n">
         <v>-17617</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-11799</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>-13036</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-11243</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>-16576</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-18808</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-10147</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14761</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>-10290</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-11349</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-10883</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-17345</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>-11986</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>-16276</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>-13192</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>-13634</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>-10289</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-14645</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-8915</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-10209</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-30876</v>
+      </c>
+      <c r="C24" t="n">
         <v>-29876</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>-19394</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>-16745</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-15804</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-14923</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-10952</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-9735</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-9917</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-6607</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-6274</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-6283</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>-5340</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-5865</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-5810</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>-5089</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>-4174</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>-4907</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-3767</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-3545</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-3385</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Acquisitions Net Of Cash Acquired And Purchases Of Intangible And Other Assets</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-258</v>
+      </c>
+      <c r="C25" t="n">
         <v>-455</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>-578</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-981</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-1405</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-1849</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-1575</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-65029</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-1186</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-301</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-679</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-349</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-18719</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-850</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-1206</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>-7512</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>-415</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>-481</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-329</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-80</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>-462</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Investments</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-12006</v>
+      </c>
+      <c r="C26" t="n">
         <v>-9845</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>-17671</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>-4474</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-2050</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-1620</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-2183</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-4258</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-8460</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-9063</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-11599</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-5013</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-8723</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-2505</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>-10309</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>-18375</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>-15092</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>-14580</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>-15910</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-19011</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-23390</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>11976</v>
+      </c>
+      <c r="C27" t="n">
         <v>12417</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>6031</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>6721</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>2604</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>2136</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>3350</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>4150</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>15718</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>13154</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>6928</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>6662</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1099</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>5253</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8862</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>15016</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>15264</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>14266</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>17247</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>11230</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>19082</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Proceeds From Investments</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>6358</v>
+      </c>
+      <c r="C28" t="n">
         <v>5691</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>3262</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>2161</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>2559</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1968</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>1941</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>1600</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>5330</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>1239</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>4775</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2711</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>16693</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>2895</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>5630</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>5876</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>2421</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>2414</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>2810</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>5370</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>6379</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>-2599</v>
+      </c>
+      <c r="C29" t="n">
         <v>-637</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>-6209</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>604</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>-16</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>-913</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>-1281</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>1347</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>-982</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>-1686</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>-301</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>-860</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>-1181</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>-89</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>-417</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>400</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>327</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>-2083</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>-27405</v>
+      </c>
+      <c r="C30" t="n">
         <v>-22705</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>-34559</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>-12714</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>-14112</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>-15201</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>-10700</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>-71925</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>503</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>-3264</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>-7150</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>-3132</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>-16171</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-1161</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>-3250</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>-9684</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>-1669</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>-5371</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>51</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-6036</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-1776</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Including Disposal Group and Discontinued Operations</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>-114</v>
+      </c>
+      <c r="C31" t="n">
         <v>11</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>-92</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>52</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>-294</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>122</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>-80</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>72</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>-99</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>29</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>88</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>-230</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>24</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>106</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>-73</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>-33</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>-46</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>-64</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>18</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>-72</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>7809</v>
+      </c>
+      <c r="C32" t="n">
         <v>-4553</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>-1393</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>11346</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>-3358</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>2525</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>2329</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>-63147</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>45748</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>10916</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>-7238</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>8953</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>-8106</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>1439</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>4941</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>-730</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>-2773</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>3629</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>2846</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-4253</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>1761</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>24296</v>
+      </c>
+      <c r="C33" t="n">
         <v>28849</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>30242</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>17482</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>20840</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>18315</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>17305</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>80452</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>34704</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>15646</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>22884</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>13931</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>20604</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>19165</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>14224</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>14432</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>17205</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>13576</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>8864</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>13117</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>11356</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Deferred Income Tax Expense (Benefit)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4446</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2491</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-2244</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-1158</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-1433</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1323</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1702</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-568</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1675</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1305</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-1191</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-198</v>
+      </c>
+      <c r="O34" t="n">
+        <v>183</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-5970</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-88</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-17</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-206</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-53</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-177</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Repayments of) Short-term Debt, Maturing in Three Months or Less</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>-5746</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H35" t="n">
         <v>-3810</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I35" t="n">
         <v>-8490</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J35" t="n">
         <v>18692</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Debt, Maturing in More than Three Months</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>6352</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I36" t="n">
         <v>10773</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J36" t="n">
         <v>7073</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Payments of Debt Restructuring Costs</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>-1754</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6215,20 +6557,20 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>45657</v>
+        <v>45747</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="C2" t="n">
         <v>594</v>
@@ -6245,202 +6587,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44561</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44196</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43921</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43830</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Total Operating Lease Liabilities</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>22238</v>
+      </c>
+      <c r="C2" t="n">
         <v>22865</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>22733</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>22924</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>21862</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>20370</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>17882</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>16942</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>16025</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>14639</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>14285</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>13884</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>13516</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>12900</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>12099</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>11148</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>10741</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>9497</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>8805</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>8788</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>8210</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Total Finance Lease Liabilities</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>62932</v>
+      </c>
+      <c r="C3" t="n">
         <v>60151</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>54434</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>39214</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>36077</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>31351</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>22905</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>20197</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>18154</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>16463</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>15584</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>14630</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>14539</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>14195</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>13548</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>12054</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>11518</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>10167</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>8610</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>8751</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>7865</v>
       </c>
     </row>
